--- a/MASTER GENERAL GIRONA OKK.xlsx
+++ b/MASTER GENERAL GIRONA OKK.xlsx
@@ -1255,7 +1255,7 @@
       <c r="I2" s="9" t="n"/>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>SAHID</t>
+          <t>SAHIL SINGH ARORA</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
@@ -1322,7 +1322,11 @@
         </is>
       </c>
       <c r="I3" s="9" t="n"/>
-      <c r="J3" s="6" t="n"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>PEDRO FERNANDEZ RIBAS</t>
+        </is>
+      </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
           <t>X-23:00 a 23:59  J,V- 23:00 a 8:00  S-00:00 a 8:00  D-23:00 a 00:00</t>
@@ -1452,7 +1456,11 @@
         </is>
       </c>
       <c r="I5" s="9" t="n"/>
-      <c r="J5" s="6" t="n"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>SAHIL SINGH ARORA</t>
+        </is>
+      </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
           <t>L-23:00 a 23:59  M,X,J- 23:00 a 8:00  V-  00:00 a 8:00</t>
@@ -1677,12 +1685,20 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>JORGE LUIS</t>
+          <t>JUAN BONADA GONZALEZ</t>
         </is>
       </c>
       <c r="I8" s="9" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>SAHIL SINGH ARORA</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Según cuadrante albergue</t>
+        </is>
+      </c>
       <c r="L8" s="18" t="n"/>
       <c r="M8" s="16" t="inlineStr">
         <is>
@@ -1742,7 +1758,11 @@
         </is>
       </c>
       <c r="I9" s="9" t="n"/>
-      <c r="J9" s="6" t="n"/>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>SAHIL SINGH ARORA</t>
+        </is>
+      </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
           <t>X 23:00 a 23:59  J,V,S de 23:00 a 8:00 y  D de 00:00 a 8:00</t>
@@ -1933,7 +1953,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAHID </t>
+          <t>SAHIL SINGH ARORA</t>
         </is>
       </c>
       <c r="I12" s="9" t="n"/>
@@ -1944,7 +1964,11 @@
         </is>
       </c>
       <c r="L12" s="18" t="n"/>
-      <c r="M12" s="16" t="n"/>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N12" s="23" t="n"/>
       <c r="O12" s="23" t="n"/>
       <c r="P12" s="23" t="n"/>
@@ -2059,7 +2083,7 @@
       </c>
       <c r="H14" s="42" t="inlineStr">
         <is>
-          <t>PEDRO CARRASCO BELMONTE</t>
+          <t>MOHAMED UAHLET</t>
         </is>
       </c>
       <c r="I14" s="59" t="inlineStr">
@@ -2067,14 +2091,22 @@
           <t>ABRIR JIRA</t>
         </is>
       </c>
-      <c r="J14" s="6" t="n"/>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>MOHAMED BELLAHCEN</t>
+        </is>
+      </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
           <t>L- 23:00 a 00:00 M,X,J de 23:00 a 8:00  S-23:00 a 00:00 D- 00:00 a  8:00</t>
         </is>
       </c>
       <c r="L14" s="18" t="n"/>
-      <c r="M14" s="16" t="n"/>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>25/09/2027</t>
+        </is>
+      </c>
       <c r="N14" s="23" t="n"/>
       <c r="O14" s="23" t="n"/>
       <c r="P14" s="23" t="n"/>
@@ -2124,8 +2156,7 @@
       </c>
       <c r="H15" s="66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASMA EL OUAHABI
-</t>
+          <t>ASMA EL OUAHABI</t>
         </is>
       </c>
       <c r="I15" s="9" t="n"/>
@@ -2210,7 +2241,7 @@
       <c r="I16" s="69" t="n"/>
       <c r="J16" s="67" t="inlineStr">
         <is>
-          <t>NIL BAZAN</t>
+          <t>NIL BAZAN SERES</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -2437,8 +2468,7 @@
       </c>
       <c r="H19" s="66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIA MOGIO MEDINA
-</t>
+          <t>ELIA MOGIO MEDINA</t>
         </is>
       </c>
       <c r="I19" s="9" t="n"/>
@@ -2519,7 +2549,7 @@
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="67" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO SOLA</t>
+          <t>JOSE ANTONIO SOLA EXPOSITO</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -2675,8 +2705,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIANO SEQUERA VACAS
-</t>
+          <t>MARIANO SEQUERA VACAS</t>
         </is>
       </c>
       <c r="I22" s="9" t="n"/>
@@ -2755,8 +2784,7 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAUL GONZALEZ EXPOSITO
-</t>
+          <t>RAUL GONZALEZ EXPOSITO</t>
         </is>
       </c>
       <c r="I23" s="9" t="n"/>
@@ -2911,7 +2939,11 @@
       </c>
       <c r="I25" s="9" t="n"/>
       <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>06:00 a 14:00</t>
+        </is>
+      </c>
       <c r="L25" s="18" t="n"/>
       <c r="M25" s="16" t="inlineStr">
         <is>
@@ -2967,7 +2999,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>SVO09390-P1-C017</t>
+          <t>SVO10033-P1-C017</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -2977,12 +3009,16 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>MARIA PILAR MOLINA</t>
+          <t>MARIA MOLINA PEREZ</t>
         </is>
       </c>
       <c r="I26" s="9" t="n"/>
       <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>07:00 a 13:00 / 12:00 a 16:30</t>
+        </is>
+      </c>
       <c r="L26" s="18" t="n"/>
       <c r="M26" s="16" t="inlineStr">
         <is>
@@ -3028,16 +3064,32 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>SVO09390-P2-C018</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="12" t="n"/>
+          <t>SVO10033-P2-C018</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>CUBIERTO</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>MARIA MOLINA PEREZ</t>
+        </is>
+      </c>
       <c r="I27" s="9" t="n"/>
       <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>L-V 07:00 a 13:00</t>
+        </is>
+      </c>
       <c r="L27" s="18" t="n"/>
-      <c r="M27" s="16" t="n"/>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N27" s="23" t="n"/>
       <c r="O27" s="23" t="n"/>
       <c r="P27" s="23" t="n"/>
@@ -3097,12 +3149,12 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>IRENE MASSANET</t>
+          <t>IRENE MASSANET MASPOCH</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>L-22:00 a 00:00 M,X,J 22:00 a 7:00 V- 00:00 a 7:00</t>
+          <t>L-V 16:00 a 21:00</t>
         </is>
       </c>
       <c r="L28" s="16" t="n"/>
@@ -3160,7 +3212,11 @@
         </is>
       </c>
       <c r="I29" s="9" t="n"/>
-      <c r="J29" s="6" t="n"/>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>JOSEP MADI ARIZA</t>
+        </is>
+      </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
           <t>L-22:00 a 00:00 M,X,J 22:00 a 7:00 V- 00:00 a 7:00</t>
@@ -3539,7 +3595,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>SVO14670-P1-C018</t>
+          <t>PROY017304-P1</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -3648,16 +3704,20 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>MOHAMMED ETTMALAH</t>
+          <t>MOHAMED BELLAHCEN</t>
         </is>
       </c>
       <c r="I35" s="9" t="n"/>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>PUNTUA</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="n"/>
+          <t>LAURA PARDILLO LOPEZ</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>Puntual según cliente</t>
+        </is>
+      </c>
       <c r="L35" s="18" t="n"/>
       <c r="M35" s="16" t="inlineStr">
         <is>
@@ -3991,25 +4051,25 @@
       </c>
       <c r="G39" s="45" t="inlineStr">
         <is>
-          <t>DESCUBIERTO</t>
+          <t>CUBIERTO</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>MOHAMED ABDELHAK DJOUMADI</t>
+          <t>MOHAMMED ETTMALAH</t>
         </is>
       </c>
       <c r="I39" s="9" t="n"/>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>JUEVES 9:15 a 11:15</t>
+          <t>JUEVES 09:15 a 11:15</t>
         </is>
       </c>
       <c r="L39" s="18" t="n"/>
       <c r="M39" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA CARMEN </t>
+          <t>Indefinido</t>
         </is>
       </c>
       <c r="N39" s="23" t="n"/>
@@ -4051,12 +4111,12 @@
       </c>
       <c r="F40" s="89" t="inlineStr">
         <is>
-          <t>PROY008324-P1</t>
+          <t>PROY08324-P2-C001</t>
         </is>
       </c>
       <c r="G40" s="45" t="inlineStr">
         <is>
-          <t>DESCUBIERTO</t>
+          <t>CUBIERTO</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -4068,7 +4128,7 @@
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>L-V  14:30 a 6:30</t>
+          <t>L-V 14:30 a 16:30</t>
         </is>
       </c>
       <c r="L40" s="18" t="n"/>
@@ -4126,8 +4186,7 @@
       </c>
       <c r="F41" s="92" t="inlineStr">
         <is>
-          <t xml:space="preserve">SVO06316-P2-C001
-</t>
+          <t>SVO06316-P2-C001</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -4137,12 +4196,20 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>MALIKA CHRIF</t>
+          <t>REDA JAIT</t>
         </is>
       </c>
       <c r="I41" s="9" t="n"/>
-      <c r="J41" s="6" t="n"/>
-      <c r="K41" s="6" t="n"/>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>SERGIO REDONDO VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>09:00 a 14:00</t>
+        </is>
+      </c>
       <c r="L41" s="18" t="n"/>
       <c r="M41" s="16" t="inlineStr">
         <is>
@@ -4267,7 +4334,11 @@
         </is>
       </c>
       <c r="I43" s="9" t="n"/>
-      <c r="K43" s="6" t="n"/>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>L-V 12:15 a 15:00</t>
+        </is>
+      </c>
       <c r="L43" s="18" t="n"/>
       <c r="M43" s="16" t="inlineStr">
         <is>
@@ -4329,10 +4400,14 @@
       <c r="I44" s="6" t="n"/>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>BLAS  P</t>
-        </is>
-      </c>
-      <c r="K44" s="6" t="n"/>
+          <t>CARLA MASSANELLAS SAURA / BLAS P</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>19:00 a 02:00</t>
+        </is>
+      </c>
       <c r="L44" s="6" t="n"/>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -4599,18 +4674,22 @@
       </c>
       <c r="H48" s="42" t="inlineStr">
         <is>
-          <t>ANWAR EL KHABBAZI RIFI</t>
+          <t>MONICA GALA SEGURA</t>
         </is>
       </c>
       <c r="I48" s="9" t="n"/>
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>15h semanales  3 veces aldia</t>
+          <t>09:00 a 12:00</t>
         </is>
       </c>
       <c r="L48" s="18" t="n"/>
-      <c r="M48" s="16" t="n"/>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>03/08/2027</t>
+        </is>
+      </c>
       <c r="N48" s="23" t="n"/>
       <c r="O48" s="23" t="n"/>
       <c r="P48" s="23" t="n"/>
@@ -4650,7 +4729,7 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>PROY018708-P1</t>
+          <t>PROY018780-P1</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -4667,7 +4746,7 @@
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>JUEVES 9:00 a 22:00</t>
+          <t>JUEVES 09:00 a 10:00</t>
         </is>
       </c>
       <c r="L49" s="18" t="n"/>
@@ -4855,11 +4934,15 @@
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
+          <t>MALIKA CHRIF</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
           <t>MOHAMED BELLAHCEN</t>
         </is>
       </c>
-      <c r="I52" s="9" t="n"/>
-      <c r="J52" s="6" t="n"/>
       <c r="K52" s="6" t="inlineStr">
         <is>
           <t>LUNES 10:00 a 11:00</t>
@@ -4868,7 +4951,7 @@
       <c r="L52" s="18" t="n"/>
       <c r="M52" s="16" t="inlineStr">
         <is>
-          <t>Indefinido</t>
+          <t>08/04/2027</t>
         </is>
       </c>
       <c r="N52" s="23" t="n"/>
@@ -4910,7 +4993,7 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>PROY018171L</t>
+          <t>PGOC018171L</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -4918,12 +5001,28 @@
           <t>CUBIERTO</t>
         </is>
       </c>
-      <c r="H53" s="9" t="n"/>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>LAURA PARDILLO LOPEZ</t>
+        </is>
+      </c>
       <c r="I53" s="9" t="n"/>
-      <c r="J53" s="6" t="n"/>
-      <c r="K53" s="6" t="n"/>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>EL HASSANE JEDDOUB</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>06:00 a 14:00</t>
+        </is>
+      </c>
       <c r="L53" s="18" t="n"/>
-      <c r="M53" s="16" t="n"/>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N53" s="23" t="n"/>
       <c r="O53" s="23" t="n"/>
       <c r="P53" s="23" t="n"/>
@@ -4963,7 +5062,7 @@
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>PROY01817J</t>
+          <t>PGOC018171J</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -4971,12 +5070,24 @@
           <t>CUBIERTO</t>
         </is>
       </c>
-      <c r="H54" s="9" t="n"/>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>MOHAMED BELLAHCEN</t>
+        </is>
+      </c>
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="6" t="n"/>
-      <c r="K54" s="6" t="n"/>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>Según cuadrante SAP HO</t>
+        </is>
+      </c>
       <c r="L54" s="18" t="n"/>
-      <c r="M54" s="16" t="n"/>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N54" s="23" t="n"/>
       <c r="O54" s="23" t="n"/>
       <c r="P54" s="23" t="n"/>
@@ -5016,7 +5127,7 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>SVO06910-P2-C001</t>
+          <t>SVO06910-P1-C018</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -5026,18 +5137,22 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>MOHAMED  . MOHA</t>
+          <t>MOHAMMED ETTMALAH</t>
         </is>
       </c>
       <c r="I55" s="9" t="n"/>
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2h semanales.</t>
+          <t>08:00 a 12:00</t>
         </is>
       </c>
       <c r="L55" s="18" t="n"/>
-      <c r="M55" s="16" t="n"/>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N55" s="23" t="n"/>
       <c r="O55" s="23" t="n"/>
       <c r="P55" s="23" t="n"/>
@@ -5152,18 +5267,22 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>MOHAMED  . MOHA</t>
+          <t>MOHAMMED ETTMALAH</t>
         </is>
       </c>
       <c r="I57" s="9" t="n"/>
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2h semanales.</t>
+          <t>12:00 a 15:00</t>
         </is>
       </c>
       <c r="L57" s="18" t="n"/>
-      <c r="M57" s="16" t="n"/>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N57" s="23" t="n"/>
       <c r="O57" s="23" t="n"/>
       <c r="P57" s="23" t="n"/>
@@ -5218,7 +5337,11 @@
       </c>
       <c r="I58" s="9" t="n"/>
       <c r="J58" s="6" t="n"/>
-      <c r="K58" s="6" t="n"/>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>L-V según cuadrante</t>
+        </is>
+      </c>
       <c r="L58" s="18" t="n"/>
       <c r="M58" s="16" t="n"/>
       <c r="N58" s="23" t="n"/>
@@ -5400,11 +5523,7 @@
       <c r="M65" s="3" t="n"/>
       <c r="N65" s="3" t="n"/>
       <c r="O65" s="3" t="n"/>
-      <c r="P65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="P65" s="3" t="n"/>
       <c r="Q65" s="3" t="n"/>
       <c r="R65" s="3" t="n"/>
       <c r="S65" s="3" t="n"/>
@@ -5417,11 +5536,7 @@
       <c r="B66" s="27" t="n"/>
       <c r="C66" s="3" t="n"/>
       <c r="D66" s="27" t="n"/>
-      <c r="F66" s="87" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="F66" s="87" t="n"/>
       <c r="G66" s="3" t="n"/>
       <c r="I66" s="26" t="n"/>
       <c r="K66" s="27" t="n"/>
@@ -5487,11 +5602,7 @@
       <c r="F69" s="87" t="n"/>
       <c r="G69" s="3" t="n"/>
       <c r="I69" s="26" t="n"/>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="J69" s="5" t="n"/>
       <c r="K69" s="27" t="n"/>
       <c r="L69" s="3" t="n"/>
       <c r="M69" s="3" t="n"/>
@@ -5534,11 +5645,7 @@
       <c r="F71" s="87" t="n"/>
       <c r="G71" s="3" t="n"/>
       <c r="I71" s="26" t="n"/>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="J71" s="5" t="n"/>
       <c r="K71" s="27" t="n"/>
       <c r="M71" s="3" t="n"/>
       <c r="N71" s="3" t="n"/>
@@ -19576,11 +19683,7 @@
     <row r="753"/>
     <row r="754"/>
     <row r="755">
-      <c r="D755" s="1" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
+      <c r="D755" s="1" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:BE738">
